--- a/experiments/results/resnet18/CIFAR-100/baseline/energy/adaptive/std/results.xlsx
+++ b/experiments/results/resnet18/CIFAR-100/baseline/energy/adaptive/std/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -1058,6 +1058,55 @@
       <c r="O14" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=None,scale_th=1.3,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>96.54000000000001</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>75.51000000000001</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>54.15</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>89.29000000000001</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>54.43</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>87.28</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>52.72</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>89.67</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>45.78</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>89.42</v>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=None,scale_th=1.5,type=std</t>
         </is>
       </c>
     </row>
